--- a/files_by_year/2022_randomsample.xlsx
+++ b/files_by_year/2022_randomsample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +16,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +48,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,96 +429,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Published Date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Embargo Release</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>File Count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>File 1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>File 2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>File 3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>File 4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>File 5</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>File 6</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>File 7</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>File 8</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>File 9</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>File 10</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>File 11</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>File 12</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>File 13</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -511,43 +532,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hq37vp68b</t>
+          <t>3n204011t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.18130/0p5s-qx29</t>
+          <t>10.18130/3jxe-nv97</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2022-12-16</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Hess_Charles_Executive Summary.pdf</t>
-        </is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hess_Charles_Prospectus.pdf</t>
+          <t>Carley_Joseph_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hess_Charles_STS_Research Paper.pdf</t>
+          <t>Carley_Joseph_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hess_Charles_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Carley_Joseph_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Carley_Joseph_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -556,50 +577,53 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6q182m105</t>
+          <t>mp48sd769</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.18130/fvpa-my73</t>
+          <t>10.18130/96jz-df36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Anderson_Luke_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>44902</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anderson_Luke_STS Research Paper.pdf</t>
+          <t>Kim_John_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anderson_Luke_Sociotechnical Synthesis.pdf</t>
+          <t>Kim_John_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Anderson_Luke_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Kim_John_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Kim_John_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -608,50 +632,51 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>p2676w587</t>
+          <t>st74cr68t</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.18130/m0nn-3863</t>
+          <t>10.18130/7xv3-0d66</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1_Metro_Andrew_2022_BS_synthesis.pdf</t>
-        </is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2_Metro_Andrew_2022_BS_tech_report.pdf</t>
+          <t>Nguyen_Phuc_2022_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3_Metro_Andrew_2022_BS_thesis.pdf</t>
+          <t>Nguyen_Phuc_2022_STS_Research.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4_Metro_Andrew_2022_BS_prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Nguyen_Phuc_2022_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nguyen_Phuc_2022_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -660,50 +685,53 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>xd07gt76f</t>
+          <t>s4655h55x</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.18130/qh9q-yd76</t>
+          <t>10.18130/bkwb-e051</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Saeed_Sania_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>44875</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saeed_Sania_STS Research Paper.pdf</t>
+          <t>Gresnick_Emily_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saeed_Sania_Sociotechnical Synthesis.pdf</t>
+          <t>Gresnick_Emily_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Saeed_Sania_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Gresnick_Emily_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Gresnick_Emily_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -712,50 +740,51 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>d791sh20h</t>
+          <t>sb3979160</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.18130/5asj-5b03</t>
+          <t>10.18130/yx0d-2e35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2022-05-05</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Anderson_Meghan_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anderson_Meghan_STS Research Paper.pdf</t>
+          <t>Sarpong_Hayden_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anderson_Meghan_Sociotechnical Synthesis.pdf</t>
+          <t>Sarpong_Hayden_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Anderson_Meghan_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sarpong_Hayden_SociotechincalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sarpong_Hayden_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -764,50 +793,51 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ht24wk38v</t>
+          <t>th83m042q</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.18130/ppe1-at69</t>
+          <t>10.18130/6t2c-yy98</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1_Chrosniak_John_2022_Sociotechnical Synthesis.pdf</t>
-        </is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2_Chrosniak_John_2022_Bouncer Locking System.pdf</t>
+          <t>Chandra_Rohan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3_Chrosniak_John_2022_Internet of Risky Things: Investigating the Social Construction of IoT Devices.pdf</t>
+          <t>Chandra_Rohan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4_Chrosniak_John_2022_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Chandra_Rohan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chandra_Rohan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -816,50 +846,53 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ff365622m</t>
+          <t>wh246t10x</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.18130/fxgc-ew68</t>
+          <t>10.18130/623e-pq79</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Brower_Anna_2022_STS Research Paper.pdf</t>
-        </is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>44878</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brower_Anna_Prospectus.pdf</t>
+          <t>Scire_Benjamin_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Brower_Anna_Sociotechnical Synthesis.pdf</t>
+          <t>Scire_Benjamin_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brower_Anna_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Scire_Benjamin_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Scire_Benjamin_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -868,50 +901,51 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8p58pf05s</t>
+          <t>j098zc29n</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.18130/z6wn-yk05</t>
+          <t>10.18130/yatf-2723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Stevens_Jamison_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stevens_Jamison_STS Research Paper.pdf</t>
+          <t>Prospectus_Ramanan_Aparna_2022_BS.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stevens_Jamison_Sociotechnical Synthesis.pdf</t>
+          <t>STS_Ramanan_Aparna_2022_BS.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Stevens_Jamison_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Technical_Ramanan_Aparna_2022_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Thesis_Ramanan_Aparna_2022_BS.pdf</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -920,50 +954,51 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>qz20st65m</t>
+          <t>02870x00h</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.18130/v0kq-3d46</t>
+          <t>10.18130/ccc5-jh50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1_Orr_Lauren_2022_BS.pdf</t>
-        </is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2_Orr_Lauren_2022_BS.pdf</t>
+          <t>Dennis_Rose_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3_Orr_Lauren_2022_BS.pdf</t>
+          <t>Dennis_Rose_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4_Orr_Lauren_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Dennis_Rose_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Dennis_Rose_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -972,50 +1007,51 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3f462644w</t>
+          <t>ht24wk458</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.18130/s11g-m234</t>
+          <t>10.18130/5pge-xy13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2022-05-05</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Wong_Wayne_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wong_Wayne_STS Research Paper.pdf</t>
+          <t>Levine_Abigail_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wong_Wayne_Sociotechnical Synthesis.pdf</t>
+          <t>Levine_Abigail_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Wong_Wayne_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Levine_Abigail_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Levine_Abigail_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1024,50 +1060,51 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3197xn158</t>
+          <t>3197xn13q</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.18130/amcz-2v98</t>
+          <t>10.18130/dt1x-xg89</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Butler_Anne Forrest_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Butler_Anne Forrest_STS Research Paper.pdf</t>
+          <t>Hoisington_Seth_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Butler_Anne Forrest_Socialtechnical Synthesis.pdf</t>
+          <t>Hoisington_Seth_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Butler_Anne Forrest_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hoisington_Seth_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hoisington_Seth_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1076,50 +1113,53 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cj82k8358</t>
+          <t>6t053h10d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.18130/ptv4-tt35</t>
+          <t>10.18130/cx8d-g997</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1_ODonnell_Piper_2022_BS.pdf</t>
-        </is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>45425</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2_ODonnell_Piper_2022_BS.pdf</t>
+          <t>Ali_Qasim_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3_ODonnell_Piper_2022_BS.pdf</t>
+          <t>Ali_Qasim_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4_ODonnell_Piper_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Ali_Qasim_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ali_Qasim_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1128,50 +1168,53 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hh63sw84z</t>
+          <t>3f462644w</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.18130/5dqt-ce95</t>
+          <t>10.18130/s11g-m234</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Klein_Darren_2022_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-05</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>45051</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klein_Darren_2022_STS_Research_Paper.pdf</t>
+          <t>Wong_Wayne_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Klein_Darren_2022_Sociotechical_Synthesis.pdf</t>
+          <t>Wong_Wayne_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Klein_Darren_2022_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Wong_Wayne_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Wong_Wayne_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1180,50 +1223,51 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9p290b30x</t>
+          <t>5d86p124w</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.18130/74hc-e026</t>
+          <t>10.18130/dtfx-v503</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Huynh_Aaron_.Prospectus.pdf</t>
-        </is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Huynh_Aaron_A Socio-technological Understanding of NASA Transferring Technology to Society.pdf</t>
+          <t>Ahmadiyar_Ryan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Huynh_Aaron_AIAA 2021-2022 Undergraduate Responsive Aerial Fire Fighting Aircraft.pdf</t>
+          <t>Ahmadiyar_Ryan_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Huynh_Aaron_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Ahmadiyar_Ryan_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ahmadiyar_Ryan_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1232,50 +1276,51 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9593tw05w</t>
+          <t>9g54xj75c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.18130/2xdg-j238</t>
+          <t>10.18130/zjdd-r617</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Patel_Darsh_Prospectus.pdf</t>
-        </is>
+          <t>2022-12-15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Patel_Darsh_STS Research Paper.pdf</t>
+          <t>Ashby_Madeleine_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Patel_Darsh_Sociotechnical Synthesis.pdf</t>
+          <t>Ashby_Madeleine_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Patel_Darsh_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Ashby_Madeleine_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ashby_Madeleine_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1284,50 +1329,53 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2j62s595m</t>
+          <t>ns064710f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.18130/h3yx-6r09</t>
+          <t>10.18130/g1y3-fy71</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Mirkhah_Bijan_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>44878</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirkhah_Bijan_STS_Research_Paper.pdf</t>
+          <t>Bruns_Patrick_A Lifesaving Pill: An Analysis of the Global Pharmaceutical Market's Impacts on Sub-Saharan Africa.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mirkhah_Bijan_Sociotechnical_Synthesis.pdf</t>
+          <t>Bruns_Patrick_Design of a Sustainable Manufacturing Process to Produce Penicillin V Using Waste Paper as a Glucose Feedstock.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Mirkhah_Bijan_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Bruns_Patrick_Prospectus.pdf</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Bruns_Patrick_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1336,50 +1384,51 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2227mq608</t>
+          <t>jq085k87b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.18130/fykc-en39</t>
+          <t>10.18130/q41r-nr62</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Williams_Chenelle_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Williams_Chenelle_STS Research Paper.pdf</t>
+          <t>Prospectus.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Williams_Chenelle_Sociotechnical Synthesis.pdf</t>
+          <t>STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Williams_Chenelle_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sociotechical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1388,50 +1437,53 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vm40xs61n</t>
+          <t>kp78gh629</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.18130/2d6p-5g85</t>
+          <t>10.18130/5pw8-xa44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Byrd_Katherine_Prospectus.pdf</t>
-        </is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>45515</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Byrd_Katherine_STS_Research_Paper.pdf</t>
+          <t>Pillari_Matthew_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Byrd_Katherine_Sociotechnical_Synthesis.pdf</t>
+          <t>Pillari_Matthew_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Byrd_Katherine_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Pillari_Matthew_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pillari_Matthew_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1440,50 +1492,51 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f4752h512</t>
+          <t>5712m754w</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.18130/bhrk-8h70</t>
+          <t>10.18130/7zzp-8998</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Zhou_Hanzhi_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhou_Hanzhi_STS Research Paper.pdf</t>
+          <t>Dickenson_Mary_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zhou_Hanzhi_Sociotechnical Synthesis.pdf</t>
+          <t>Dickenson_Mary_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Zhou_Hanzhi_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Dickenson_Mary_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Dickenson_Mary_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1492,50 +1545,51 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6m311q347</t>
+          <t>q524jp79w</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.18130/hkp4-er49</t>
+          <t>10.18130/pdd0-6s47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2022-12-16</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1_Rauf_Fayzan_2022_BS.pdf</t>
-        </is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2_Rauf_Fayzan_2022_BS.pdf</t>
+          <t>Moccia_Kevin_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3_Rauf_Fayzan_2022_BS.pdf</t>
+          <t>Moccia_Kevin_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4_Rauf_Fayzan_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Moccia_Kevin_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Moccia_Kevin_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1544,50 +1598,51 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44558f37b</t>
+          <t>kd17ct85n</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.18130/63v9-zy21</t>
+          <t>10.18130/x22a-9d52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Rafiq_Noor_Prospectus.pdf</t>
-        </is>
+          <t>2022-12-17</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rafiq_Noor_STS_Research_Paper.pdf</t>
+          <t>Kim_Edward_Prospectus_Final.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rafiq_Noor_Sociotechnical_Synthesis.pdf</t>
+          <t>Kim_Edward_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Rafiq_Noor_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Kim_Edward_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Kim_Edward_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1596,50 +1651,51 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vx021f95d</t>
+          <t>2227mq73b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.18130/8w4c-th23</t>
+          <t>10.18130/thrc-v297</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Ruppert_Nathaniel_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ruppert_Nathaniel_STS Research Paper.pdf</t>
+          <t>Lee_Pyung_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ruppert_Nathaniel_Sociotechnical Synthesis.pdf</t>
+          <t>Lee_Pyung_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ruppert_Nathaniel_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Lee_Pyung_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Lee_Pyung_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1648,50 +1704,51 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hq37vp558</t>
+          <t>rr171z18r</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.18130/rtm1-5a85</t>
+          <t>10.18130/0fdj-g734</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Steenrod_Conner_Prospectus</t>
-        </is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Steenrod_Conner_STSResearchPaper</t>
+          <t>Kim_Zachary_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Steenrod_Conner_SociotechnicalSynthesis</t>
+          <t>Kim_Zachary_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Steenrod_Conner_TechnicalReport</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Kim_Zachary_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Kim_Zachary_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1700,50 +1757,51 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gt54kn98f</t>
+          <t>2j62s594b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.18130/eej2-2s20</t>
+          <t>10.18130/5etd-a251</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Jennings_Gabrielle_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jennings_Gabrielle_STS Research Paper.pdf</t>
+          <t>Kwon_Christopher_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jennings_Gabrielle_Sociotechnical Synthesis.pdf</t>
+          <t>Kwon_Christopher_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Jennings_Gabrielle_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Kwon_Christopher_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Kwon_Christopher_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1752,50 +1810,53 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ww72bc50w</t>
+          <t>37720d83t</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.18130/ce87-dj48</t>
+          <t>10.18130/7r3v-7b29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Wray_Jackson_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>44878</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wray_Jackson_STS Research Paper.pdf</t>
+          <t>Lloyd_Cole_DESIGN OF COST-EFFECTIVE AND ACCURATE LASER CUTTER THAT SERVES A MARKET NICHE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Wray_Jackson_Sociotechnical Synthesis.pdf</t>
+          <t>Lloyd_Cole_Prospectus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Wray_Jackson_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Lloyd_Cole_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Lloyd_Cole_USING AUTONOMOUS ELECTRIC VEHICLES TO PROMOTE SUSTAINABILITY</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1804,50 +1865,51 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nz806066j</t>
+          <t>zk51vh68v</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.18130/mgjd-jz79</t>
+          <t>10.18130/a587-6245</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Byrd_Alexander_Automated Ball Launcher for Alleviation of Pet Canine Separation Anxiety.pdf</t>
-        </is>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Byrd_Alexander_Prospectus.pdf</t>
+          <t>Chen_Christos_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Byrd_Alexander_Sociotechnical Synthesis.pdf</t>
+          <t>Chen_Christos_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Byrd_Alexander_The Future of Tumor Reversion Therapy: How Society Decides the Interpretation of a Technology.pdf</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Chen_Christos_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Chen_Christos_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1856,50 +1918,51 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>c821gk740</t>
+          <t>3197xn158</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.18130/ekjj-yd21</t>
+          <t>10.18130/amcz-2v98</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Wiler_Jonathan_Classified Information and Ethical Obligations.pdf</t>
-        </is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wiler_Jonathan_Cybersecurity in National Defense: Understanding Adversarial Capabilities.pdf</t>
+          <t>Butler_Anne Forrest_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Wiler_Jonathan_Prospectus.pdf</t>
+          <t>Butler_Anne Forrest_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Wiler_Jonathan_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Butler_Anne Forrest_Socialtechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Butler_Anne Forrest_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1908,50 +1971,51 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>z316q252w</t>
+          <t>b8515p287</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10.18130/80m9-p372</t>
+          <t>10.18130/gzwa-6795</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Harrington_Justin_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harrington_Justin_STS Research Paper.pdf</t>
+          <t>Prospectus_Zhao_Catherine_2022_BS.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Harrington_Justin_SociotechnicalSynthesis.pdf</t>
+          <t>STS_Research_Paper_Zhao_Catherine_2022_BS.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Harrington_Justin_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Sociotechnical_Synthesis_Zhao_Catherine_2022_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Technical_Report_Zhao_Catherine_2022_BS.pdf</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -1960,50 +2024,51 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>m900nv43g</t>
+          <t>w66344481</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10.18130/afhr-hg88</t>
+          <t>10.18130/1gdx-7k38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Yang_Matthew_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yang_Matthew_STS Research Paper.pdf</t>
+          <t>Surti_Shivani_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yang_Matthew_Sociotechnical Synthesis.pdf</t>
+          <t>Surti_Shivani_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Yang_Matthew_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Surti_Shivani_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Surti_Shivani_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2012,19 +2077,20 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2z10wr20m</t>
+          <t>vm40xs572</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10.18130/vc95-mn65</t>
+          <t>10.18130/cxzh-xc16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2032,30 +2098,30 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Grasmeder_Sarah_Prospectus.pdf</t>
-        </is>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grasmeder_Sarah_STS Research Paper.pdf</t>
+          <t>1_Perez_Carlos_2022_BS.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Grasmeder_Sarah_Sociotechnical Synthesis.pdf</t>
+          <t>2_Perez_Carlos_2022_BS.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Grasmeder_Sarah_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>3_Perez_Carlos_2022_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4_Perez_Carlos_2022_BS.pdf</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2064,50 +2130,51 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>m326m288h</t>
+          <t>7m01bm622</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10.18130/h45y-3k43</t>
+          <t>10.18130/y9pv-jm89</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2022-12-17</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Kharitonashvili_Eric_Executive_Summary.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kharitonashvili_Eric_Prospectus.pdf</t>
+          <t>Handa_Rishub_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kharitonashvili_Eric_STS_Research_Paper.pdf</t>
+          <t>Handa_Rishub_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kharitonashvili_Eric_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Handa_Rishub_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Handa_Rishub_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2116,50 +2183,51 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>st74cr67j</t>
+          <t>sx61dn36s</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.18130/tbma-2s25</t>
+          <t>10.18130/jjfc-kr53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Prospectus_Hamilton_Christopher_2022_BS.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>STS_Research_Paper_Hamilton_Christopher_2022_BS.pdf</t>
+          <t>Wolcott_Emma_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sociotechnical_Synthesis_Hamilton_Christopher_2022_BS.pdf</t>
+          <t>Wolcott_Emma_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Technical_Report_Hamilton_Christopher_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Wolcott_Emma_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Wolcott_Emma_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2168,50 +2236,51 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ns064708d</t>
+          <t>vx021f95d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.18130/91bx-zs60</t>
+          <t>10.18130/8w4c-th23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Morales_Gabriel_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Morales_Gabriel_STS Research Paper.pdf</t>
+          <t>Ruppert_Nathaniel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Morales_Gabriel_Sociotechnical Synthesis.pdf</t>
+          <t>Ruppert_Nathaniel_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Morales_Gabriel_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Ruppert_Nathaniel_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Ruppert_Nathaniel_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2220,50 +2289,53 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5m60qs93d</t>
+          <t>rr171z20s</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.18130/z2aa-ea25</t>
+          <t>10.18130/4ak9-3x08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Zyglowicz_Noal_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>45052</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zyglowicz_Noal_STS Research Report.pdf</t>
+          <t>Winans_Nicholas_Cryptographically Secure Encryption Using Adversarial Neural Networks.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Zyglowicz_Noal_Sociotechnical Synthesis.pdf</t>
+          <t>Winans_Nicholas_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Zyglowicz_Noal_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Winans_Nicholas_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Winans_Nicholas_The Presence of Unintended Bias in Artificial Learning Used in The Hiring Process.pdf</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2272,50 +2344,51 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5t34sk33q</t>
+          <t>0v838189z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10.18130/7c84-cw24</t>
+          <t>10.18130/c725-qf96</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Quezada_John_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quezada_John_STS_Research_Paper.pdf</t>
+          <t>Cyber-Physical Systems and National Security - Executive Summary and ToC.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Quezada_John_Sociotechnical_Synthesis.pdf</t>
+          <t>Cyber-Physical Systems and National Security - Prospectus.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Quezada_John_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Cyber-Physical Systems and National Security - STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Cyber-Physical Systems and National Security - Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2324,50 +2397,53 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3r074w115</t>
+          <t>jh343t42f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10.18130/mdjq-qp97</t>
+          <t>10.18130/2j70-ya67</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Chander_Janani_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-03</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chander_Janani_STS Research Paper.pdf</t>
+          <t>Breen_Charles_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chander_Janani_Sociotechnical Synthesis.pdf</t>
+          <t>Breen_Charles_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Chander_Janani_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Breen_Charles_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Breen_Charles_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2376,50 +2452,53 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2v23vv40v</t>
+          <t>9593tw022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10.18130/wyr2-p526</t>
+          <t>10.18130/33cy-7r53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Weatherford_Zoe_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Weatherford_Zoe_STSResearch.pdf</t>
+          <t>Back_Roan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Weatherford_Zoe_Sociotechnical.pdf</t>
+          <t>Back_Roan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Weatherford_Zoe_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Back_Roan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Back_Roan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2428,50 +2507,51 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dv13zv10w</t>
+          <t>2227mq608</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10.18130/mp9e-7763</t>
+          <t>10.18130/fykc-en39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Lee_Gordon_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lee_Gordon_STS Research Paper.pdf</t>
+          <t>Williams_Chenelle_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lee_Gordon_Sociotechnical Synthesis.pdf</t>
+          <t>Williams_Chenelle_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lee_Gordon_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Williams_Chenelle_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Williams_Chenelle_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2480,50 +2560,51 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0c483k590</t>
+          <t>mk61rh993</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.18130/xkg3-bp59</t>
+          <t>10.18130/npgp-eg04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Prospectus_Karumuri_Harish_2022_BS.pdf</t>
-        </is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>STS_Karumuri_Harish_2022_BS.pdf</t>
+          <t>Riewerts_Christian_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Synthesis_Karumuri_Harish_2022_BS.pdf</t>
+          <t>Riewerts_Christian_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Technical_Karumuri_Harish_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Riewerts_Christian_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Riewerts_Christian_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2532,19 +2613,20 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>zc77sr09d</t>
+          <t>tt44pn77f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.18130/3eb5-8s66</t>
+          <t>10.18130/d3v9-xh03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2552,30 +2634,30 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Notz_Mason_Prospectus.pdf</t>
-        </is>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Notz_Mason_STS Research Paper.pdf</t>
+          <t>Thota_Vineeth_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Notz_Mason_Sociotechnical Synthesis.pdf</t>
+          <t>Thota_Vineeth_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Notz_Mason_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Thota_Vineeth_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Thota_Vineeth_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2584,50 +2666,51 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tq57nr954</t>
+          <t>3t945r69k</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10.18130/7n83-cr36</t>
+          <t>10.18130/fz8j-st03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Martin_Derek_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Martin_Derek_STS Research Paper.pdf</t>
+          <t>Alwine_Madeleine_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Martin_Derek_Sociotechnical Synthesis.pdf</t>
+          <t>Alwine_Madeleine_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Martin_Derek_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Alwine_Madeleine_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Alwine_Madeleine_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2636,19 +2719,20 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>g158bj32g</t>
+          <t>4m90dw52h</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10.18130/j8z4-fq64</t>
+          <t>10.18130/0b5y-xy02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2656,30 +2740,30 @@
           <t>2022-05-09</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>1_Graham_Julia_2022_BS.pdf</t>
-        </is>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2_Graham_Julia_2022_BS.pdf</t>
+          <t>Wu_Michelle_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3_Graham_Julia_2022_BS.pdf</t>
+          <t>Wu_Michelle_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4_Graham_Julia_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Wu_Michelle_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Wu_Michelle_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2688,50 +2772,51 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="n">
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1544bq02z</t>
+          <t>h702q744d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.18130/wx8s-sp62</t>
+          <t>10.18130/dt66-5d93</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Runyan_Matthew_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Runyan_Matthew_STSResearchPaper.pdf</t>
+          <t>1_Lee_Rachel_2022_BS.pdf</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Runyan_Matthew_SociotechnicalSynthesis.pdf</t>
+          <t>2_Lee_Rachel_2022_BS.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Runyan_Matthew_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>3_Lee_Rachel_2022_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4_Lee_Rachel_2022_BS.pdf</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2740,50 +2825,53 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="n">
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jm214q21x</t>
+          <t>7w62f924m</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.18130/djvd-6k26</t>
+          <t>10.18130/qv18-r569</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2022-12-13</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Chang_Angus_Prospectus.pdf</t>
-        </is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>44968</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chang_Angus_STS Research Paper.pdf</t>
+          <t>Davis_Cameron_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chang_Angus_Sociotechnical Synthesis.pdf</t>
+          <t>Davis_Cameron_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Chang_Angus_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Davis_Cameron_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Davis_Cameron_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2792,50 +2880,51 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sx61dn372</t>
+          <t>1544bq02z</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10.18130/kp9h-mf45</t>
+          <t>10.18130/wx8s-sp62</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Dozier_Claire_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dozier_Claire_STS Research Paper.pdf</t>
+          <t>Runyan_Matthew_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dozier_Claire_Sociotechnical Synthesis.pdf</t>
+          <t>Runyan_Matthew_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Dozier_Claire_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Runyan_Matthew_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Runyan_Matthew_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2844,50 +2933,51 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>zg64tm972</t>
+          <t>k3569517w</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10.18130/8jng-g320</t>
+          <t>10.18130/y9fy-qh15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Williams_Trevor_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Williams_Trevor_STS Research Paper.pdf</t>
+          <t>Pande_Radhika_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Williams_Trevor_Sociotechnical Synthesis.pdf</t>
+          <t>Pande_Radhika_STS ResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Williams_Trevor_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Pande_Radhika_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Pande_Radhika_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2896,50 +2986,51 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="n">
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>wm117p99c</t>
+          <t>wp988k783</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10.18130/sek2-z632</t>
+          <t>10.18130/77r6-t364</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Liu_Justin_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liu_Justin_STS_Research_Paper.pdf</t>
+          <t>Huynh_Lillian_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Liu_Justin_Sociotechnical_Synthesis.pdf</t>
+          <t>Huynh_Lillian_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Liu_Justin_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Huynh_Lillian_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Huynh_Lillian_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2948,50 +3039,51 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4m90dw585</t>
+          <t>vm40xs61n</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10.18130/ktpg-gy12</t>
+          <t>10.18130/2d6p-5g85</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Rodriguez_Pedro_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rodriguez_Pedro_STS Research Paper.pdf</t>
+          <t>Byrd_Katherine_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rodriguez_Pedro_Sociotechnical Synthesis.pdf</t>
+          <t>Byrd_Katherine_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Rodriguez_Pedro_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Byrd_Katherine_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Byrd_Katherine_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3000,50 +3092,51 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="n">
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2227mq71s</t>
+          <t>9s1617152</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10.18130/y68n-p132</t>
+          <t>10.18130/s1xa-wk50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Prospectus_Dawkins_Maximilian_2022_BS.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>STS_Research_Paper_Dawkins_Maximilian_2022_BS.pdf</t>
+          <t>Wu_Wei_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sociotechnical_Synthesis_Dawkins_Maximilian_2022_BS.pdf</t>
+          <t>Wu_Wei_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Technical_Report_Dawkins_Maximilian_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Wu_Wei_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Wu_Wei_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3052,50 +3145,51 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="n">
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>c821gk83z</t>
+          <t>wh246t205</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10.18130/c25a-6827</t>
+          <t>10.18130/ra0q-4w39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Nguyen_Lena_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nguyen_Lena_STS Research Paper.pdf</t>
+          <t>Wiele_Emily_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nguyen_Lena_Sociotechnical Synthesis.pdf</t>
+          <t>Wiele_Emily_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nguyen_Lena_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Wiele_Emily_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Wiele_Emily_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3104,50 +3198,51 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>v979v414x</t>
+          <t>k930bx92j</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10.18130/fjvx-y534</t>
+          <t>10.18130/637j-j567</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Weigand_Christopher_Optimizing for Water Equity in the Colorado River Basin.pdf</t>
-        </is>
+          <t>2022-05-05</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>4</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Weigand_Christopher_Prospectus.pdf</t>
+          <t>Humphreys_Kieran_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Weigand_Christopher_Sociotechnical Synthesis.pdf</t>
+          <t>Humphreys_Kieran_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Weigand_Christopher_Strategies Employed by Cancer Alley Advocates to Pursue Environmental Justice in Their Communities.pdf</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Humphreys_Kieran_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Humphreys_Kieran_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3156,50 +3251,53 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>h702q741k</t>
+          <t>db78td023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10.18130/dy2d-6360</t>
+          <t>10.18130/942h-bc28</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Ko_Grace_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>45052</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ko_Grace_STS Research Paper.pdf</t>
+          <t>Scruggs_Cristian_Data Bias Considerations for Artificial Intelligence Systems in Higher Education.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ko_Grace_Sociotechnical Synthesis.pdf</t>
+          <t>Scruggs_Cristian_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Ko_Grace_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Scruggs_Cristian_Satori: A Course Management System.pdf</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Scruggs_Cristian_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3208,50 +3306,51 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2z10wr21w</t>
+          <t>4m90dw585</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10.18130/sayd-m087</t>
+          <t>10.18130/ktpg-gy12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Barrington_Nathaniel Prospectus.pdf</t>
-        </is>
+          <t>2022-05-15</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Barrington_Nathaniel_STS Research Paper.pdf</t>
+          <t>Rodriguez_Pedro_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Barrington_Nathaniel_Sociotechnical Synthesis.pdf</t>
+          <t>Rodriguez_Pedro_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Barrington_Nathaniel_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Rodriguez_Pedro_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Rodriguez_Pedro_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3260,50 +3359,51 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>th83m042q</t>
+          <t>j3860783m</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10.18130/6t2c-yy98</t>
+          <t>10.18130/3n3w-7c88</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Chandra_Rohan_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chandra_Rohan_STS Research Paper.pdf</t>
+          <t>Yates_Rachel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chandra_Rohan_Sociotechnical Synthesis.pdf</t>
+          <t>Yates_Rachel_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Chandra_Rohan_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Yates_Rachel_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Yates_Rachel_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3312,50 +3412,51 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="n">
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
         <v>2022</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3197xn069</t>
+          <t>f1881m88g</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10.18130/bywn-k566</t>
+          <t>10.18130/t78t-k247</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Vidlak_Grace_Prospectus.pdf</t>
-        </is>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vidlak_Grace_STS Research Paper.pdf</t>
+          <t>KormathAnand_Rithika_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Vidlak_Grace_Sociotechnical Synthesis.pdf</t>
+          <t>KormathAnand_Rithika_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Vidlak_Grace_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>KormathAnand_Rithika_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>KormathAnand_Rithika_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3364,631 +3465,8 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>xd07gt74w</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>10.18130/ygca-cx10</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>sx61dn36s</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>10.18130/jjfc-kr53</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Wolcott_Emma_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Wolcott_Emma_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Wolcott_Emma_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Wolcott_Emma_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>gx41mj81h</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>10.18130/ntyw-3z48</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Lynch_Annabel_Prospectus</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Lynch_Annabel_STS Research Paper</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Lynch_Annabel_Sociotechnical Synthesis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Lynch_Annabel_Technical Report</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>hd76s092k</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>10.18130/qq5k-1313</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Prospectus_Boland_Alexander_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>STSResearchPaper_Boland_Alexander_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>SocioTechnicalSynthesis_Boland_Alexander_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>TechnicalReport_Boland_Alexander_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>7w62f920h</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>10.18130/rzft-eh28</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>1_Cauthen_Joshua_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2_Cauthen_Joshua_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>3_Cauthen_Joshua_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>4_Cauthen_Joshua_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>736665751</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>10.18130/tswr-zf33</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Shamsie_Hafsah_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Shamsie_Hafsah_STSResearchPaper.pdf</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Shamsie_Hafsah_SociotechnicalSynthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Shamsie_Hafsah_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>4q77fs28z</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>10.18130/1j83-xr71</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Mulquin_William_Automatic Smart Pet Feeding Station.pdf</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Mulquin_William_Examining Smart Home Technology Effectiveness and the User Onboarding Processes.pdf</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Mulquin_William_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Mulquin_William_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>02870w875</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>10.18130/2zyw-en79</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Prospectus</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Research Paper</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Sociotechnical Synthesis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Technical Report</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>76537226b</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>10.18130/8eex-mq74</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Kerns_Sophia_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Kerns_Sophia_STSResearchPaper.pdf</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Kerns_Sophia_SociotechnicalSynthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kerns_Sophia_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>p5547s401</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>10.18130/aqjp-cq05</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Rachamallu_Medhini_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Rachamallu_Medhini_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Rachamallu_Medhini_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Rachamallu_Medhini_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>zp38wd541</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>10.18130/js3b-aj32</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>1_Gardner_Devin_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2_Gardner_Devin_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>3_Gardner_Devin_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>4_Gardner_Devin_2022_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ws859g569</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>10.18130/6m10-wb17</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Doyle_Caroline_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Doyle_Caroline_STS_Research_Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Doyle_Caroline_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Doyle_Caroline_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
         <v>2022</v>
       </c>
     </row>
